--- a/Templates/bulkImport/config/construct_MS_config_sslr.xlsx
+++ b/Templates/bulkImport/config/construct_MS_config_sslr.xlsx
@@ -1,163 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\inetpub\wwwroot\RI_V3\Templates\bulkImport\config\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40E03067-0FFC-496B-80C9-461B1D5B5DCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="23040" windowHeight="9024"/>
   </bookViews>
   <sheets>
     <sheet name="construct_MS_config_sarawak" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>Asus</author>
-  </authors>
-  <commentList>
-    <comment ref="H5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Times New Roman"/>
-          </rPr>
-          <t>Value must be
-"HSET" / "Quality"
-"HSET;Quality"</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="M5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Times New Roman"/>
-          </rPr>
-          <t>Date Format:
-2024-01-01</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="T5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Times New Roman"/>
-          </rPr>
-          <t xml:space="preserve">Date Format:
-2024-01-01
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AA5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Times New Roman"/>
-          </rPr>
-          <t xml:space="preserve">Date Format:
-2024-01-01
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AB5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Times New Roman"/>
-          </rPr>
-          <t>Value must be
-"Yes" / "No"</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AH5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Times New Roman"/>
-          </rPr>
-          <t xml:space="preserve">Date Format:
-2024-01-01
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AI5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Times New Roman"/>
-          </rPr>
-          <t>Value must be:
-"Yes" / "No"</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AO5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000008000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Times New Roman"/>
-          </rPr>
-          <t xml:space="preserve">Date Format:
-2024-01-01
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AT5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000009000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Times New Roman"/>
-          </rPr>
-          <t xml:space="preserve">Date Format:
-2024-01-01
-</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="80">
   <si>
     <t>*</t>
   </si>
   <si>
+    <t>Show</t>
+  </si>
+  <si>
     <t>show</t>
   </si>
   <si>
     <t>Hidden</t>
   </si>
   <si>
-    <t>Show</t>
-  </si>
-  <si>
     <t>c_ref_no</t>
   </si>
   <si>
@@ -233,46 +103,7 @@
     <t>c_acknowledge_date</t>
   </si>
   <si>
-    <t>provide_comment</t>
-  </si>
-  <si>
-    <t>commenter_remark</t>
-  </si>
-  <si>
-    <t>commenter_name</t>
-  </si>
-  <si>
-    <t>commenter_position</t>
-  </si>
-  <si>
-    <t>commenter_company</t>
-  </si>
-  <si>
-    <t>commenter_time</t>
-  </si>
-  <si>
-    <t>commenter_date</t>
-  </si>
-  <si>
-    <t>provide_comment2</t>
-  </si>
-  <si>
-    <t>commenter_remark2</t>
-  </si>
-  <si>
-    <t>commenter_name2</t>
-  </si>
-  <si>
-    <t>commenter_position2</t>
-  </si>
-  <si>
-    <t>commenter_company2</t>
-  </si>
-  <si>
-    <t>commenter_time2</t>
-  </si>
-  <si>
-    <t>commenter_date2</t>
+    <t>c_tsrs_no</t>
   </si>
   <si>
     <t>c_reviewer_comment</t>
@@ -284,119 +115,55 @@
     <t>c_require_resubmission</t>
   </si>
   <si>
+    <t>c_review_attachment</t>
+  </si>
+  <si>
     <t>c_reviewed_by</t>
   </si>
   <si>
     <t>c_reviewed_date</t>
   </si>
   <si>
+    <t>c_acknowledge2</t>
+  </si>
+  <si>
+    <t>c_acknowledge_name2</t>
+  </si>
+  <si>
+    <t>c_acknowledge_position2</t>
+  </si>
+  <si>
+    <t>c_acknowledge_company2</t>
+  </si>
+  <si>
+    <t>c_acknowledge_time2</t>
+  </si>
+  <si>
+    <t>c_acknowledge_date2</t>
+  </si>
+  <si>
     <t>c_close_remark</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">Reference No. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>*</t>
-    </r>
+    <t>Reference No.</t>
   </si>
   <si>
     <t>Section</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">Action </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>*</t>
-    </r>
+    <t>Action</t>
   </si>
   <si>
     <t>Revision No.</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">Subject </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>*</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">Category </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>*</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">Work Discipline </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>*</t>
-    </r>
+    <t>Subject</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Work Discipline</t>
   </si>
   <si>
     <t>Description/Details</t>
@@ -405,44 +172,10 @@
     <t>File</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">Issued By </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>*</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">Issued Date </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>*</t>
-    </r>
+    <t>Issued By</t>
+  </si>
+  <si>
+    <t>Issued Date</t>
   </si>
   <si>
     <t>Remarks</t>
@@ -457,9 +190,6 @@
     <t>Coordinate</t>
   </si>
   <si>
-    <t>Action</t>
-  </si>
-  <si>
     <t>Actioner</t>
   </si>
   <si>
@@ -487,25 +217,7 @@
     <t>Acknowledge Date (RE)</t>
   </si>
   <si>
-    <t>Provide Comment?</t>
-  </si>
-  <si>
-    <t>Comment</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Position</t>
-  </si>
-  <si>
-    <t>Organization</t>
-  </si>
-  <si>
-    <t>Time</t>
-  </si>
-  <si>
-    <t>Date</t>
+    <t>TSRS No.</t>
   </si>
   <si>
     <t>Reviewer's Comment</t>
@@ -517,43 +229,44 @@
     <t>Resubmission Required</t>
   </si>
   <si>
+    <t>Review File</t>
+  </si>
+  <si>
     <t>Reviewed By</t>
   </si>
   <si>
     <t>Reviewed Date</t>
   </si>
   <si>
+    <t>Acknowledger Name (SO)</t>
+  </si>
+  <si>
+    <t>Acknowledger Position (SO)</t>
+  </si>
+  <si>
+    <t>Acknowledger Company (SO)</t>
+  </si>
+  <si>
+    <t>Acknowledge Time (SO)</t>
+  </si>
+  <si>
+    <t>Acknowledge Date (SO)</t>
+  </si>
+  <si>
     <t>Close Remarks</t>
-  </si>
-  <si>
-    <t>c_ref_no_rev_no</t>
-  </si>
-  <si>
-    <t>c_site_doc_ref_no</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Ref. No with Rev. No. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>*</t>
-    </r>
-  </si>
-  <si>
-    <t>Site Document Reference No.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
+  <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;RM&quot;* #,##0.00_-;\-&quot;RM&quot;* #,##0.00_-;_-&quot;RM&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;RM&quot;* #,##0_-;\-&quot;RM&quot;* #,##0_-;_-&quot;RM&quot;* &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -562,24 +275,351 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="Times New Roman"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -587,24 +627,310 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -891,73 +1217,73 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AU5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:AM5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="17.109375" customWidth="1"/>
-    <col min="2" max="2" width="9.33203125" customWidth="1"/>
-    <col min="3" max="4" width="13.44140625" customWidth="1"/>
-    <col min="5" max="5" width="20.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="25.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.33203125" customWidth="1"/>
-    <col min="8" max="8" width="10.44140625" customWidth="1"/>
-    <col min="9" max="9" width="17" customWidth="1"/>
-    <col min="10" max="10" width="18.44140625" customWidth="1"/>
-    <col min="11" max="11" width="13.109375" customWidth="1"/>
-    <col min="12" max="12" width="11.6640625" customWidth="1"/>
-    <col min="13" max="13" width="13.6640625" customWidth="1"/>
-    <col min="14" max="14" width="20.44140625" customWidth="1"/>
-    <col min="15" max="16" width="7.44140625" customWidth="1"/>
-    <col min="17" max="17" width="13.44140625" customWidth="1"/>
-    <col min="18" max="20" width="21.88671875" customWidth="1"/>
-    <col min="21" max="21" width="15.33203125" customWidth="1"/>
-    <col min="22" max="22" width="14.6640625" customWidth="1"/>
-    <col min="23" max="23" width="27.44140625" customWidth="1"/>
-    <col min="24" max="24" width="25.6640625" customWidth="1"/>
-    <col min="25" max="25" width="26.88671875" customWidth="1"/>
-    <col min="26" max="26" width="22.33203125" customWidth="1"/>
-    <col min="27" max="41" width="23.44140625" customWidth="1"/>
-    <col min="42" max="42" width="20.5546875" customWidth="1"/>
-    <col min="43" max="43" width="17" customWidth="1"/>
-    <col min="44" max="44" width="22.6640625" customWidth="1"/>
-    <col min="45" max="45" width="14.5546875" customWidth="1"/>
-    <col min="46" max="46" width="16.44140625" customWidth="1"/>
-    <col min="47" max="47" width="14.88671875" customWidth="1"/>
+    <col min="1" max="1" width="13.8888888888889" customWidth="1"/>
+    <col min="2" max="2" width="9.33333333333333" customWidth="1"/>
+    <col min="3" max="4" width="13.4444444444444" customWidth="1"/>
+    <col min="5" max="5" width="9.33333333333333" customWidth="1"/>
+    <col min="6" max="6" width="10.4444444444444" customWidth="1"/>
+    <col min="7" max="7" width="17" customWidth="1"/>
+    <col min="8" max="8" width="18.4444444444444" customWidth="1"/>
+    <col min="9" max="9" width="13.1111111111111" customWidth="1"/>
+    <col min="10" max="10" width="11.6666666666667" customWidth="1"/>
+    <col min="11" max="11" width="13.6666666666667" customWidth="1"/>
+    <col min="12" max="12" width="20.4444444444444" customWidth="1"/>
+    <col min="13" max="14" width="7.44444444444444" customWidth="1"/>
+    <col min="15" max="15" width="13.4444444444444" customWidth="1"/>
+    <col min="16" max="18" width="21.8888888888889" customWidth="1"/>
+    <col min="19" max="19" width="6.44444444444444" customWidth="1"/>
+    <col min="20" max="20" width="14.6666666666667" customWidth="1"/>
+    <col min="21" max="21" width="20.8888888888889" customWidth="1"/>
+    <col min="22" max="22" width="23.3333333333333" customWidth="1"/>
+    <col min="23" max="23" width="24" customWidth="1"/>
+    <col min="24" max="24" width="20" customWidth="1"/>
+    <col min="25" max="25" width="19.8888888888889" customWidth="1"/>
+    <col min="26" max="26" width="9.33333333333333" customWidth="1"/>
+    <col min="27" max="27" width="20.5555555555556" customWidth="1"/>
+    <col min="28" max="28" width="17" customWidth="1"/>
+    <col min="29" max="29" width="22.6666666666667" customWidth="1"/>
+    <col min="30" max="30" width="20.4444444444444" customWidth="1"/>
+    <col min="31" max="31" width="14.5555555555556" customWidth="1"/>
+    <col min="32" max="32" width="16.4444444444444" customWidth="1"/>
+    <col min="33" max="33" width="15.6666666666667" customWidth="1"/>
+    <col min="34" max="34" width="22" customWidth="1"/>
+    <col min="35" max="35" width="24.3333333333333" customWidth="1"/>
+    <col min="36" max="36" width="25" customWidth="1"/>
+    <col min="37" max="37" width="21" customWidth="1"/>
+    <col min="38" max="38" width="20.8888888888889" customWidth="1"/>
+    <col min="39" max="39" width="14.8888888888889" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:47" ht="15" customHeight="1">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
+    <row r="1" spans="3:11">
       <c r="C1" t="s">
         <v>0</v>
       </c>
       <c r="E1" t="s">
         <v>0</v>
       </c>
+      <c r="F1" t="s">
+        <v>0</v>
+      </c>
       <c r="G1" t="s">
         <v>0</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>0</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>0</v>
       </c>
-      <c r="L1" t="s">
-        <v>0</v>
-      </c>
-      <c r="M1" t="s">
-        <v>0</v>
-      </c>
     </row>
-    <row r="2" spans="1:47" ht="15" customHeight="1">
+    <row r="2" spans="1:39">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -965,19 +1291,19 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" t="s">
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H2" t="s">
         <v>1</v>
@@ -986,22 +1312,22 @@
         <v>1</v>
       </c>
       <c r="J2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L2" t="s">
         <v>1</v>
       </c>
       <c r="M2" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N2" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P2" t="s">
         <v>2</v>
@@ -1010,10 +1336,10 @@
         <v>2</v>
       </c>
       <c r="R2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T2" t="s">
         <v>1</v>
@@ -1055,7 +1381,7 @@
         <v>1</v>
       </c>
       <c r="AG2" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AH2" t="s">
         <v>1</v>
@@ -1073,34 +1399,10 @@
         <v>1</v>
       </c>
       <c r="AM2" t="s">
-        <v>3</v>
-      </c>
-      <c r="AN2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AO2" t="s">
-        <v>3</v>
-      </c>
-      <c r="AP2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AQ2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AR2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AS2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AT2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AU2" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:47" ht="15" customHeight="1">
+    <row r="3" spans="1:39">
       <c r="A3">
         <v>0</v>
       </c>
@@ -1218,32 +1520,8 @@
       <c r="AM3">
         <v>38</v>
       </c>
-      <c r="AN3">
-        <v>39</v>
-      </c>
-      <c r="AO3">
-        <v>40</v>
-      </c>
-      <c r="AP3">
-        <v>41</v>
-      </c>
-      <c r="AQ3">
-        <v>42</v>
-      </c>
-      <c r="AR3">
-        <v>43</v>
-      </c>
-      <c r="AS3">
-        <v>44</v>
-      </c>
-      <c r="AT3">
-        <v>45</v>
-      </c>
-      <c r="AU3">
-        <v>46</v>
-      </c>
     </row>
-    <row r="4" spans="1:47" ht="15" customHeight="1">
+    <row r="4" spans="1:39">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -1257,282 +1535,234 @@
         <v>7</v>
       </c>
       <c r="E4" t="s">
-        <v>87</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>88</v>
+        <v>9</v>
       </c>
       <c r="G4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="N4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="O4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="P4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="Q4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="R4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="S4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="T4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="U4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="V4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="W4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="X4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Y4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="Z4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AA4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AB4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="AC4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AD4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="AE4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AF4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="AG4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AH4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="AI4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AJ4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="AK4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AL4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AM4" t="s">
-        <v>40</v>
-      </c>
-      <c r="AN4" t="s">
-        <v>41</v>
-      </c>
-      <c r="AO4" t="s">
         <v>42</v>
       </c>
-      <c r="AP4" t="s">
+    </row>
+    <row r="5" spans="1:39">
+      <c r="A5" t="s">
         <v>43</v>
       </c>
-      <c r="AQ4" t="s">
+      <c r="B5" t="s">
         <v>44</v>
       </c>
-      <c r="AR4" t="s">
+      <c r="C5" t="s">
         <v>45</v>
       </c>
-      <c r="AS4" t="s">
+      <c r="D5" t="s">
         <v>46</v>
       </c>
-      <c r="AT4" t="s">
+      <c r="E5" t="s">
         <v>47</v>
       </c>
-      <c r="AU4" t="s">
+      <c r="F5" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="5" spans="1:47" ht="15" customHeight="1">
-      <c r="A5" t="s">
+      <c r="G5" t="s">
         <v>49</v>
       </c>
-      <c r="B5" t="s">
+      <c r="H5" t="s">
         <v>50</v>
       </c>
-      <c r="C5" t="s">
+      <c r="I5" t="s">
         <v>51</v>
       </c>
-      <c r="D5" t="s">
+      <c r="J5" t="s">
         <v>52</v>
       </c>
-      <c r="E5" t="s">
-        <v>89</v>
-      </c>
-      <c r="F5" t="s">
-        <v>90</v>
-      </c>
-      <c r="G5" t="s">
+      <c r="K5" t="s">
         <v>53</v>
       </c>
-      <c r="H5" t="s">
+      <c r="L5" t="s">
         <v>54</v>
       </c>
-      <c r="I5" t="s">
+      <c r="M5" t="s">
         <v>55</v>
       </c>
-      <c r="J5" t="s">
+      <c r="N5" t="s">
         <v>56</v>
       </c>
-      <c r="K5" t="s">
+      <c r="O5" t="s">
         <v>57</v>
       </c>
-      <c r="L5" t="s">
+      <c r="P5" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q5" t="s">
         <v>58</v>
       </c>
-      <c r="M5" t="s">
+      <c r="R5" t="s">
         <v>59</v>
       </c>
-      <c r="N5" t="s">
+      <c r="S5" t="s">
         <v>60</v>
       </c>
-      <c r="O5" t="s">
+      <c r="T5" t="s">
         <v>61</v>
       </c>
-      <c r="P5" t="s">
+      <c r="U5" t="s">
         <v>62</v>
       </c>
-      <c r="Q5" t="s">
+      <c r="V5" t="s">
         <v>63</v>
       </c>
-      <c r="R5" t="s">
+      <c r="W5" t="s">
         <v>64</v>
       </c>
-      <c r="S5" t="s">
+      <c r="X5" t="s">
         <v>65</v>
       </c>
-      <c r="T5" t="s">
+      <c r="Y5" t="s">
         <v>66</v>
       </c>
-      <c r="U5" t="s">
+      <c r="Z5" t="s">
         <v>67</v>
       </c>
-      <c r="V5" t="s">
+      <c r="AA5" t="s">
         <v>68</v>
       </c>
-      <c r="W5" t="s">
+      <c r="AB5" t="s">
         <v>69</v>
       </c>
-      <c r="X5" t="s">
+      <c r="AC5" t="s">
         <v>70</v>
       </c>
-      <c r="Y5" t="s">
+      <c r="AD5" t="s">
         <v>71</v>
       </c>
-      <c r="Z5" t="s">
+      <c r="AE5" t="s">
         <v>72</v>
       </c>
-      <c r="AA5" t="s">
+      <c r="AF5" t="s">
         <v>73</v>
       </c>
-      <c r="AB5" t="s">
+      <c r="AG5" t="s">
+        <v>61</v>
+      </c>
+      <c r="AH5" t="s">
         <v>74</v>
       </c>
-      <c r="AC5" t="s">
+      <c r="AI5" t="s">
         <v>75</v>
       </c>
-      <c r="AD5" t="s">
+      <c r="AJ5" t="s">
         <v>76</v>
       </c>
-      <c r="AE5" t="s">
+      <c r="AK5" t="s">
         <v>77</v>
       </c>
-      <c r="AF5" t="s">
+      <c r="AL5" t="s">
         <v>78</v>
       </c>
-      <c r="AG5" t="s">
+      <c r="AM5" t="s">
         <v>79</v>
-      </c>
-      <c r="AH5" t="s">
-        <v>80</v>
-      </c>
-      <c r="AI5" t="s">
-        <v>74</v>
-      </c>
-      <c r="AJ5" t="s">
-        <v>75</v>
-      </c>
-      <c r="AK5" t="s">
-        <v>76</v>
-      </c>
-      <c r="AL5" t="s">
-        <v>77</v>
-      </c>
-      <c r="AM5" t="s">
-        <v>78</v>
-      </c>
-      <c r="AN5" t="s">
-        <v>79</v>
-      </c>
-      <c r="AO5" t="s">
-        <v>80</v>
-      </c>
-      <c r="AP5" t="s">
-        <v>81</v>
-      </c>
-      <c r="AQ5" t="s">
-        <v>82</v>
-      </c>
-      <c r="AR5" t="s">
-        <v>83</v>
-      </c>
-      <c r="AS5" t="s">
-        <v>84</v>
-      </c>
-      <c r="AT5" t="s">
-        <v>85</v>
-      </c>
-      <c r="AU5" t="s">
-        <v>86</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
+  <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertRows="0" insertColumns="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>